--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.74382678706784</v>
+        <v>6.945871852898524</v>
       </c>
       <c r="D2" t="n">
-        <v>42.85251856108951</v>
+        <v>6.963534266177046</v>
       </c>
       <c r="E2" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F2" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.91694365582101</v>
+        <v>7.786503344070914</v>
       </c>
       <c r="D3" t="n">
-        <v>47.30770174751095</v>
+        <v>7.687501533970529</v>
       </c>
       <c r="E3" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F3" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.48472606954781</v>
+        <v>4.46626798630152</v>
       </c>
       <c r="D4" t="n">
-        <v>27.04173513117757</v>
+        <v>4.394281958816356</v>
       </c>
       <c r="E4" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F4" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.87363145546436</v>
+        <v>5.016965111512959</v>
       </c>
       <c r="D5" t="n">
-        <v>32.88723987269731</v>
+        <v>5.344176479313313</v>
       </c>
       <c r="E5" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F5" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.77552050478614</v>
+        <v>4.026022082027748</v>
       </c>
       <c r="D6" t="n">
-        <v>24.77180585632549</v>
+        <v>4.025418451652892</v>
       </c>
       <c r="E6" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F6" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.75304741404993</v>
+        <v>2.884870204783113</v>
       </c>
       <c r="D7" t="n">
-        <v>23.26784997033242</v>
+        <v>3.781025620179019</v>
       </c>
       <c r="E7" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F7" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.64303055628994</v>
+        <v>3.516992465397115</v>
       </c>
       <c r="D8" t="n">
-        <v>22.01193629379923</v>
+        <v>3.576939647742376</v>
       </c>
       <c r="E8" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F8" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.96241948735541</v>
+        <v>6.006393166695255</v>
       </c>
       <c r="D9" t="n">
-        <v>37.57179446903479</v>
+        <v>6.105416601218154</v>
       </c>
       <c r="E9" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F9" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47508217643237</v>
+        <v>4.46470085367026</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33066115243998</v>
+        <v>4.116232437271496</v>
       </c>
       <c r="E10" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F10" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.22923476177757</v>
+        <v>2.962250648788856</v>
       </c>
       <c r="D11" t="n">
-        <v>40.97243655858741</v>
+        <v>6.658020940770455</v>
       </c>
       <c r="E11" t="n">
-        <v>9.640120050963457</v>
+        <v>1.566519508281562</v>
       </c>
       <c r="F11" t="n">
-        <v>8.71865902602136</v>
+        <v>1.416782091728471</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
